--- a/viewer/downloads/CPM_Standards_Alignment_Master.xlsx
+++ b/viewer/downloads/CPM_Standards_Alignment_Master.xlsx
@@ -734,8 +734,8 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,10 +801,14 @@
           <t>9.3.6.5, 9.3.7.10, 9.3.7.2, 9.3.7.6, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr"/>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.B.7, 8.G.2, see ebook</t>
+        </is>
+      </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -839,10 +843,14 @@
           <t>9.3.5.6, 9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.3, 9.3.6.5, 9.3.7.1, 9.3.7.2, 9.3.7.3</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr"/>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.4a, 7.EE.A.1.A, 7.EE.A.1.B, 7.SP.8a, 7.Sp.8a, 8.EE.C.7.A, see ebook</t>
+        </is>
+      </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -877,10 +885,14 @@
           <t>9.3.5.7, 9.3.5.8, 9.3.6.1, 9.3.6.4, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr"/>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.3, 7.EE.4b, 7.SP.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -915,10 +927,14 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -953,10 +969,14 @@
           <t>9.3.5.9, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>8.G.C.1</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -991,10 +1011,14 @@
           <t>9.3.6.5</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr"/>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>see ebook</t>
+        </is>
+      </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1077,10 +1101,14 @@
           <t>9.3.7.1, 9.3.7.2, 9.3.7.3</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr"/>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1131,14 @@
           <t>9.2.3.7, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr"/>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>7.Sp.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1129,10 +1161,14 @@
           <t>9.3.7.3, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr"/>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.B, 8.G.C.1</t>
+        </is>
+      </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1155,10 +1191,14 @@
           <t>9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr"/>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 8.EE.A.8</t>
+        </is>
+      </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1181,10 +1221,14 @@
           <t>9.3.5.3, 9.3.6.5</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr"/>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.8b, see ebook</t>
+        </is>
+      </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1233,10 +1277,14 @@
           <t>9.1.1.1, 9.1.1.12, 9.1.1.14, 9.1.1.15, 9.1.1.2, 9.1.1.3, 9.1.1.4, 9.1.1.5</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr"/>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>6.EE.A.2.A, 6.EE.A.2.B, 6.EE.A.3, 6.NS.B.4, 6.NS.C.6.C, 6.NS.C.7.C, MP 1, MP 7</t>
+        </is>
+      </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1259,10 +1307,14 @@
           <t>9.1.1.5</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr"/>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>6.EE.A.3</t>
+        </is>
+      </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1281,10 +1333,14 @@
           <t>9.1.1.10, 9.1.1.13, 9.1.1.7, 9.1.1.9</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr"/>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.A, 6.NS.C.7.A, 6.NS.C.7.B, 6.NS.C.7.D</t>
+        </is>
+      </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1333,10 +1389,14 @@
           <t>9.3.7.4, 9.3.7.5, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr"/>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B, 8.EE.B.8, 8.G.B.1</t>
+        </is>
+      </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1355,10 +1415,14 @@
           <t>9.1.2.6, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr"/>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>8.G.B.1</t>
+        </is>
+      </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1381,10 +1445,14 @@
           <t>9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr"/>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.8a</t>
+        </is>
+      </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1407,10 +1475,14 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr"/>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1445,10 +1517,14 @@
           <t>9.1.2.4</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr"/>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>6.RP.3c</t>
+        </is>
+      </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1471,10 +1547,14 @@
           <t>9.1.1.8</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr"/>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.B</t>
+        </is>
+      </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1523,10 +1603,14 @@
           <t>9.3.7.9</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr"/>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>8.G.C.1</t>
+        </is>
+      </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1567,10 +1651,14 @@
           <t>9.3.6.3, 9.3.7.10, 9.3.7.2, 9.3.7.3, 9.3.7.6</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr"/>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.4a, 7.EE.A.1.A, 7.EE.A.1.B, 8.EE.B.7, 8.G.2</t>
+        </is>
+      </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1594,8 +1682,8 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1687,10 +1775,14 @@
           <t>9.2.4.12, 9.2.4.6</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr"/>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>7.RP.A.2.D, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1713,10 +1805,14 @@
           <t>9.2.4.1, 9.2.4.12, 9.2.4.13, 9.2.4.14</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr"/>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.A, 7.SP.7a, 7.SP.7b, 7.SP.7c</t>
+        </is>
+      </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1751,10 +1847,14 @@
           <t>9.2.4.1, 9.2.4.12, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.A, 7.RP.A.2.B, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1777,10 +1877,14 @@
           <t>9.2.3.6, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1815,10 +1919,14 @@
           <t>9.2.3.9</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.D</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1853,10 +1961,14 @@
           <t>9.2.3.3, 9.2.3.8, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr"/>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.7a, 7.SP.C.7.B, 7.SP.C.8.A</t>
+        </is>
+      </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1887,10 +1999,14 @@
           <t>9.2.3.3, 9.2.3.8</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr"/>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.C.7.B, 7.SP.C.8.A</t>
+        </is>
+      </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1909,10 +2025,14 @@
           <t>9.1.2.8, 9.2.3.2, 9.2.3.3</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr"/>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.D, 7.SP.C.7.B, 7.SP.C.8.C</t>
+        </is>
+      </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1931,10 +2051,14 @@
           <t>9.2.3.2, 9.2.3.3</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr"/>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.D, 7.SP.C.7.B</t>
+        </is>
+      </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1965,10 +2089,14 @@
           <t>9.2.4.10, 9.2.4.4, 9.2.4.5, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr"/>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.C, 7.RP.3, 7.RP.A.2.A, 7.RP.A.2.B</t>
+        </is>
+      </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1987,10 +2115,14 @@
           <t>9.2.3.1, 9.2.4.10</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr"/>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>7.RP.3, 8.EE.C.7.B</t>
+        </is>
+      </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2025,10 +2157,14 @@
           <t>9.1.2.1, 9.1.2.2, 9.1.2.3, 9.1.2.4, 9.1.2.7</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr"/>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>6.EE.A.2.C, 6.EE.A.4, 6.G.1, 6.RP.3c, Review skills needed for 6.NS.1</t>
+        </is>
+      </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2047,10 +2183,14 @@
           <t>9.2.4.15</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr"/>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.6</t>
+        </is>
+      </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2069,10 +2209,14 @@
           <t>9.2.4.3, 9.2.4.4, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr"/>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.A, 7.NS.A.2.C, 7.RP.A.2.B</t>
+        </is>
+      </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2091,10 +2235,14 @@
           <t>9.2.3.1</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr"/>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.B</t>
+        </is>
+      </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2147,10 +2295,14 @@
           <t>9.2.4.10, 9.2.4.11, 9.2.4.12, 9.2.4.4, 9.2.4.6, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr"/>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.C, 7.RP.3, 7.RP.A.2.B, 7.RP.A.2.D, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2169,10 +2321,14 @@
           <t>9.2.3.3, 9.2.4.1, 9.2.4.12, 9.2.4.15, 9.2.4.3</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr"/>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.A, 7.NS.A.2.A, 7.SP.6, 7.SP.7a, 7.SP.C.7.B</t>
+        </is>
+      </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2191,10 +2347,14 @@
           <t>9.2.3.9</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr"/>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.D</t>
+        </is>
+      </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2213,10 +2373,14 @@
           <t>9.2.4.3</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr"/>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.2.A</t>
+        </is>
+      </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2251,10 +2415,14 @@
           <t>9.2.3.3, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr"/>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.7a, 7.SP.C.7.B</t>
+        </is>
+      </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2273,10 +2441,14 @@
           <t>9.2.3.4, 9.2.3.9</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr"/>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.D, 7.SP.C.7.A</t>
+        </is>
+      </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2295,10 +2467,14 @@
           <t>9.2.4.1, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr"/>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.A, 7.SP.7a</t>
+        </is>
+      </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2329,10 +2505,14 @@
           <t>9.2.4.8, 9.2.4.9</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr"/>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.C, 7.RP.A.2.C</t>
+        </is>
+      </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2351,10 +2531,14 @@
           <t>9.1.2.1, 9.1.2.3, 9.1.2.5</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr"/>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>6.EE.A.4, 6.NS.3, Review skills needed for 6.NS.1</t>
+        </is>
+      </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2373,10 +2557,14 @@
           <t>9.1.2.1</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr"/>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>6.EE.A.4</t>
+        </is>
+      </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2407,10 +2595,14 @@
           <t>9.2.3.4, 9.2.3.5</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr"/>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.C.7.A, Prep for 7.SP.C.8.A</t>
+        </is>
+      </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2429,10 +2621,14 @@
           <t>9.2.3.5, 9.2.4.12, 9.2.4.8, 9.2.4.9</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr"/>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>7.NS.A.1.C, 7.RP.A.2.C, 7.SP.7a, Prep for 7.SP.C.8.A</t>
+        </is>
+      </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2463,10 +2659,14 @@
           <t>9.2.3.3, 9.2.4.12, 9.3.6.6</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr"/>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.7a, 7.SP.C.7.B, MP4</t>
+        </is>
+      </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17455,8 +17655,8 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17522,10 +17722,14 @@
           <t>9.3.6.7, 9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr"/>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17560,10 +17764,14 @@
           <t>9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr"/>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17586,10 +17794,14 @@
           <t>9.2.3.6, 9.3.7.1, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr"/>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 8.EE.A.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17642,10 +17854,14 @@
           <t>9.3.5.8, 9.3.6.1, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.3, 7.SP.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17680,10 +17896,14 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17706,10 +17926,14 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr"/>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17744,10 +17968,14 @@
           <t>9.3.7.1, 9.3.7.4, 9.3.7.5</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr"/>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B, 8.EE.B.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17770,10 +17998,14 @@
           <t>9.3.7.4, 9.3.7.5</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr"/>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B, 8.EE.B.8</t>
+        </is>
+      </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17796,10 +18028,14 @@
           <t>9.3.5.5, 9.3.7.1, 9.3.7.4, 9.3.7.5, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr"/>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B, 8.EE.A.8, 8.EE.B.8, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17834,10 +18070,14 @@
           <t>9.1.1.11, 9.1.1.6, 9.2.3.6, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr"/>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 6.RP.A.3.C, 7.Sp.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17860,10 +18100,14 @@
           <t>9.1.1.11, 9.1.1.15, 9.1.1.5, 9.1.1.6, 9.1.1.8, 9.2.3.6, 9.3.5.6</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr"/>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 6.EE.A.2.A, 6.EE.A.3, 6.NS.C.6.B, 6.RP.A.3.C, 7.Sp.8a</t>
+        </is>
+      </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17898,10 +18142,14 @@
           <t>9.3.7.10, 9.3.7.2, 9.3.7.3, 9.3.7.6, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr"/>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.A.8, 8.EE.B.7, 8.G.2</t>
+        </is>
+      </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17924,10 +18172,14 @@
           <t>9.2.3.6, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr"/>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 7.Sp.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17950,10 +18202,14 @@
           <t>9.2.3.6, 9.3.7.1, 9.3.7.2, 9.3.7.6, 9.3.7.7, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr"/>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 7.EE.A.1.A, 8.EE.A.8, 8.EE.B.7, 8.EE.C.7.A, 8.G.B.1</t>
+        </is>
+      </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17976,10 +18232,14 @@
           <t>9.3.5.2, 9.3.5.6, 9.3.6.8, 9.3.7.1, 9.3.7.2</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr"/>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 7.Sp.8a, 8.EE.C.7.A, MP8</t>
+        </is>
+      </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18014,10 +18274,14 @@
           <t>9.2.3.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr"/>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18040,10 +18304,14 @@
           <t>9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.4</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr"/>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.4b, 7.SP.8a</t>
+        </is>
+      </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18066,10 +18334,14 @@
           <t>9.2.3.6, 9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.3, 9.3.6.5, 9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr"/>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>5.NF.A.1, 7.EE.4a, 7.EE.A.1.A, 7.SP.8a, 8.EE.A.8, 8.EE.C.7.A, see ebook</t>
+        </is>
+      </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18104,10 +18376,14 @@
           <t>9.3.6.3, 9.3.6.5</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr"/>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.4a, see ebook</t>
+        </is>
+      </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18130,10 +18406,14 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr"/>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18174,10 +18454,14 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr"/>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18212,10 +18496,14 @@
           <t>9.1.2.5</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr"/>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>6.NS.3</t>
+        </is>
+      </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18238,10 +18526,14 @@
           <t>9.3.5.3, 9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr"/>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.8a, 7.SP.8b</t>
+        </is>
+      </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18282,10 +18574,14 @@
           <t>9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr"/>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>7.SP.8a</t>
+        </is>
+      </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18320,10 +18616,14 @@
           <t>9.3.7.2, 9.3.7.3, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr"/>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.G.C.1</t>
+        </is>
+      </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18346,10 +18646,14 @@
           <t>9.1.1.10, 9.1.1.13, 9.1.1.7, 9.1.1.9</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr"/>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.A, 6.NS.C.7.A, 6.NS.C.7.B, 6.NS.C.7.D</t>
+        </is>
+      </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18372,10 +18676,14 @@
           <t>9.2.3.7, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr"/>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CPM_Standards_Alignment_Master.xlsx
+++ b/viewer/downloads/CPM_Standards_Alignment_Master.xlsx
@@ -734,8 +734,8 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,14 +801,10 @@
           <t>9.3.6.5, 9.3.7.10, 9.3.7.2, 9.3.7.6, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.B.7, 8.G.2, see ebook</t>
-        </is>
-      </c>
+      <c r="E3" s="13" t="inlineStr"/>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -843,14 +839,10 @@
           <t>9.3.5.6, 9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.3, 9.3.6.5, 9.3.7.1, 9.3.7.2, 9.3.7.3</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.4a, 7.EE.A.1.A, 7.EE.A.1.B, 7.SP.8a, 7.Sp.8a, 8.EE.C.7.A, see ebook</t>
-        </is>
-      </c>
+      <c r="E5" s="13" t="inlineStr"/>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -885,14 +877,10 @@
           <t>9.3.5.7, 9.3.5.8, 9.3.6.1, 9.3.6.4, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.3, 7.EE.4b, 7.SP.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -927,14 +915,10 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -969,14 +953,10 @@
           <t>9.3.5.9, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>8.G.C.1</t>
-        </is>
-      </c>
+      <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1011,14 +991,10 @@
           <t>9.3.6.5</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>see ebook</t>
-        </is>
-      </c>
+      <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1101,14 +1077,10 @@
           <t>9.3.7.1, 9.3.7.2, 9.3.7.3</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E18" s="13" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1131,14 +1103,10 @@
           <t>9.2.3.7, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>7.Sp.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E19" s="13" t="inlineStr"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1161,14 +1129,10 @@
           <t>9.3.7.3, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.B, 8.G.C.1</t>
-        </is>
-      </c>
+      <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1155,10 @@
           <t>9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 8.EE.A.8</t>
-        </is>
-      </c>
+      <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1221,14 +1181,10 @@
           <t>9.3.5.3, 9.3.6.5</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.8b, see ebook</t>
-        </is>
-      </c>
+      <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1277,14 +1233,10 @@
           <t>9.1.1.1, 9.1.1.12, 9.1.1.14, 9.1.1.15, 9.1.1.2, 9.1.1.3, 9.1.1.4, 9.1.1.5</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>6.EE.A.2.A, 6.EE.A.2.B, 6.EE.A.3, 6.NS.B.4, 6.NS.C.6.C, 6.NS.C.7.C, MP 1, MP 7</t>
-        </is>
-      </c>
+      <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1307,14 +1259,10 @@
           <t>9.1.1.5</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>6.EE.A.3</t>
-        </is>
-      </c>
+      <c r="E26" s="13" t="inlineStr"/>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1333,14 +1281,10 @@
           <t>9.1.1.10, 9.1.1.13, 9.1.1.7, 9.1.1.9</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.A, 6.NS.C.7.A, 6.NS.C.7.B, 6.NS.C.7.D</t>
-        </is>
-      </c>
+      <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1389,14 +1333,10 @@
           <t>9.3.7.4, 9.3.7.5, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B, 8.EE.B.8, 8.G.B.1</t>
-        </is>
-      </c>
+      <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1415,14 +1355,10 @@
           <t>9.1.2.6, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>8.G.B.1</t>
-        </is>
-      </c>
+      <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1445,14 +1381,10 @@
           <t>9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.8a</t>
-        </is>
-      </c>
+      <c r="E32" s="13" t="inlineStr"/>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1475,14 +1407,10 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1517,14 +1445,10 @@
           <t>9.1.2.4</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>6.RP.3c</t>
-        </is>
-      </c>
+      <c r="E35" s="13" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1547,14 +1471,10 @@
           <t>9.1.1.8</t>
         </is>
       </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.B</t>
-        </is>
-      </c>
+      <c r="E36" s="13" t="inlineStr"/>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1603,14 +1523,10 @@
           <t>9.3.7.9</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>8.G.C.1</t>
-        </is>
-      </c>
+      <c r="E39" s="13" t="inlineStr"/>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1651,14 +1567,10 @@
           <t>9.3.6.3, 9.3.7.10, 9.3.7.2, 9.3.7.3, 9.3.7.6</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.4a, 7.EE.A.1.A, 7.EE.A.1.B, 8.EE.B.7, 8.G.2</t>
-        </is>
-      </c>
+      <c r="E41" s="13" t="inlineStr"/>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1682,8 +1594,8 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1775,14 +1687,10 @@
           <t>9.2.4.12, 9.2.4.6</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>7.RP.A.2.D, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E5" s="13" t="inlineStr"/>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1805,14 +1713,10 @@
           <t>9.2.4.1, 9.2.4.12, 9.2.4.13, 9.2.4.14</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.A, 7.SP.7a, 7.SP.7b, 7.SP.7c</t>
-        </is>
-      </c>
+      <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1847,14 +1751,10 @@
           <t>9.2.4.1, 9.2.4.12, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.A, 7.RP.A.2.B, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1877,14 +1777,10 @@
           <t>9.2.3.6, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1919,14 +1815,10 @@
           <t>9.2.3.9</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.D</t>
-        </is>
-      </c>
+      <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1961,14 +1853,10 @@
           <t>9.2.3.3, 9.2.3.8, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.7a, 7.SP.C.7.B, 7.SP.C.8.A</t>
-        </is>
-      </c>
+      <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1999,14 +1887,10 @@
           <t>9.2.3.3, 9.2.3.8</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.C.7.B, 7.SP.C.8.A</t>
-        </is>
-      </c>
+      <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2025,14 +1909,10 @@
           <t>9.1.2.8, 9.2.3.2, 9.2.3.3</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.D, 7.SP.C.7.B, 7.SP.C.8.C</t>
-        </is>
-      </c>
+      <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2051,14 +1931,10 @@
           <t>9.2.3.2, 9.2.3.3</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.D, 7.SP.C.7.B</t>
-        </is>
-      </c>
+      <c r="E17" s="13" t="inlineStr"/>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2089,14 +1965,10 @@
           <t>9.2.4.10, 9.2.4.4, 9.2.4.5, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.C, 7.RP.3, 7.RP.A.2.A, 7.RP.A.2.B</t>
-        </is>
-      </c>
+      <c r="E19" s="13" t="inlineStr"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2115,14 +1987,10 @@
           <t>9.2.3.1, 9.2.4.10</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>7.RP.3, 8.EE.C.7.B</t>
-        </is>
-      </c>
+      <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2157,14 +2025,10 @@
           <t>9.1.2.1, 9.1.2.2, 9.1.2.3, 9.1.2.4, 9.1.2.7</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>6.EE.A.2.C, 6.EE.A.4, 6.G.1, 6.RP.3c, Review skills needed for 6.NS.1</t>
-        </is>
-      </c>
+      <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2183,14 +2047,10 @@
           <t>9.2.4.15</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.6</t>
-        </is>
-      </c>
+      <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2209,14 +2069,10 @@
           <t>9.2.4.3, 9.2.4.4, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.A, 7.NS.A.2.C, 7.RP.A.2.B</t>
-        </is>
-      </c>
+      <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2235,14 +2091,10 @@
           <t>9.2.3.1</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.B</t>
-        </is>
-      </c>
+      <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2295,14 +2147,10 @@
           <t>9.2.4.10, 9.2.4.11, 9.2.4.12, 9.2.4.4, 9.2.4.6, 9.2.4.7</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.C, 7.RP.3, 7.RP.A.2.B, 7.RP.A.2.D, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2321,14 +2169,10 @@
           <t>9.2.3.3, 9.2.4.1, 9.2.4.12, 9.2.4.15, 9.2.4.3</t>
         </is>
       </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.A, 7.NS.A.2.A, 7.SP.6, 7.SP.7a, 7.SP.C.7.B</t>
-        </is>
-      </c>
+      <c r="E29" s="13" t="inlineStr"/>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2347,14 +2191,10 @@
           <t>9.2.3.9</t>
         </is>
       </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.D</t>
-        </is>
-      </c>
+      <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2373,14 +2213,10 @@
           <t>9.2.4.3</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.2.A</t>
-        </is>
-      </c>
+      <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2415,14 +2251,10 @@
           <t>9.2.3.3, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.7a, 7.SP.C.7.B</t>
-        </is>
-      </c>
+      <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2441,14 +2273,10 @@
           <t>9.2.3.4, 9.2.3.9</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.D, 7.SP.C.7.A</t>
-        </is>
-      </c>
+      <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2467,14 +2295,10 @@
           <t>9.2.4.1, 9.2.4.12</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.A, 7.SP.7a</t>
-        </is>
-      </c>
+      <c r="E35" s="13" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2505,14 +2329,10 @@
           <t>9.2.4.8, 9.2.4.9</t>
         </is>
       </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.C, 7.RP.A.2.C</t>
-        </is>
-      </c>
+      <c r="E37" s="13" t="inlineStr"/>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2531,14 +2351,10 @@
           <t>9.1.2.1, 9.1.2.3, 9.1.2.5</t>
         </is>
       </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>6.EE.A.4, 6.NS.3, Review skills needed for 6.NS.1</t>
-        </is>
-      </c>
+      <c r="E38" s="13" t="inlineStr"/>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2557,14 +2373,10 @@
           <t>9.1.2.1</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>6.EE.A.4</t>
-        </is>
-      </c>
+      <c r="E39" s="13" t="inlineStr"/>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2595,14 +2407,10 @@
           <t>9.2.3.4, 9.2.3.5</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.C.7.A, Prep for 7.SP.C.8.A</t>
-        </is>
-      </c>
+      <c r="E41" s="13" t="inlineStr"/>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2621,14 +2429,10 @@
           <t>9.2.3.5, 9.2.4.12, 9.2.4.8, 9.2.4.9</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>7.NS.A.1.C, 7.RP.A.2.C, 7.SP.7a, Prep for 7.SP.C.8.A</t>
-        </is>
-      </c>
+      <c r="E42" s="13" t="inlineStr"/>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2659,14 +2463,10 @@
           <t>9.2.3.3, 9.2.4.12, 9.3.6.6</t>
         </is>
       </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.7a, 7.SP.C.7.B, MP4</t>
-        </is>
-      </c>
+      <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17655,8 +17455,8 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17722,14 +17522,10 @@
           <t>9.3.6.7, 9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E3" s="13" t="inlineStr"/>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17764,14 +17560,10 @@
           <t>9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E5" s="13" t="inlineStr"/>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17794,14 +17586,10 @@
           <t>9.2.3.6, 9.3.7.1, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 8.EE.A.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17854,14 +17642,10 @@
           <t>9.3.5.8, 9.3.6.1, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.3, 7.SP.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17896,14 +17680,10 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17926,14 +17706,10 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E12" s="13" t="inlineStr"/>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17968,14 +17744,10 @@
           <t>9.3.7.1, 9.3.7.4, 9.3.7.5</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B, 8.EE.B.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E14" s="13" t="inlineStr"/>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17770,10 @@
           <t>9.3.7.4, 9.3.7.5</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B, 8.EE.B.8</t>
-        </is>
-      </c>
+      <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18028,14 +17796,10 @@
           <t>9.3.5.5, 9.3.7.1, 9.3.7.4, 9.3.7.5, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B, 8.EE.A.8, 8.EE.B.8, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18070,14 +17834,10 @@
           <t>9.1.1.11, 9.1.1.6, 9.2.3.6, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 6.RP.A.3.C, 7.Sp.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E18" s="13" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18100,14 +17860,10 @@
           <t>9.1.1.11, 9.1.1.15, 9.1.1.5, 9.1.1.6, 9.1.1.8, 9.2.3.6, 9.3.5.6</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 6.EE.A.2.A, 6.EE.A.3, 6.NS.C.6.B, 6.RP.A.3.C, 7.Sp.8a</t>
-        </is>
-      </c>
+      <c r="E19" s="13" t="inlineStr"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18142,14 +17898,10 @@
           <t>9.3.7.10, 9.3.7.2, 9.3.7.3, 9.3.7.6, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.A.8, 8.EE.B.7, 8.G.2</t>
-        </is>
-      </c>
+      <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18172,14 +17924,10 @@
           <t>9.2.3.6, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 7.Sp.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18202,14 +17950,10 @@
           <t>9.2.3.6, 9.3.7.1, 9.3.7.2, 9.3.7.6, 9.3.7.7, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 7.EE.A.1.A, 8.EE.A.8, 8.EE.B.7, 8.EE.C.7.A, 8.G.B.1</t>
-        </is>
-      </c>
+      <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18232,14 +17976,10 @@
           <t>9.3.5.2, 9.3.5.6, 9.3.6.8, 9.3.7.1, 9.3.7.2</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 7.Sp.8a, 8.EE.C.7.A, MP8</t>
-        </is>
-      </c>
+      <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18274,14 +18014,10 @@
           <t>9.2.3.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E26" s="13" t="inlineStr"/>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18304,14 +18040,10 @@
           <t>9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.4</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.4b, 7.SP.8a</t>
-        </is>
-      </c>
+      <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18334,14 +18066,10 @@
           <t>9.2.3.6, 9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.3, 9.3.6.5, 9.3.7.1, 9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>5.NF.A.1, 7.EE.4a, 7.EE.A.1.A, 7.SP.8a, 8.EE.A.8, 8.EE.C.7.A, see ebook</t>
-        </is>
-      </c>
+      <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18376,14 +18104,10 @@
           <t>9.3.6.3, 9.3.6.5</t>
         </is>
       </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.4a, see ebook</t>
-        </is>
-      </c>
+      <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18406,14 +18130,10 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18454,14 +18174,10 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18496,14 +18212,10 @@
           <t>9.1.2.5</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>6.NS.3</t>
-        </is>
-      </c>
+      <c r="E35" s="13" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18526,14 +18238,10 @@
           <t>9.3.5.3, 9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.8a, 7.SP.8b</t>
-        </is>
-      </c>
+      <c r="E36" s="13" t="inlineStr"/>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18574,14 +18282,10 @@
           <t>9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>7.SP.8a</t>
-        </is>
-      </c>
+      <c r="E38" s="13" t="inlineStr"/>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18616,14 +18320,10 @@
           <t>9.3.7.2, 9.3.7.3, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E40" s="19" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.G.C.1</t>
-        </is>
-      </c>
+      <c r="E40" s="13" t="inlineStr"/>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18646,14 +18346,10 @@
           <t>9.1.1.10, 9.1.1.13, 9.1.1.7, 9.1.1.9</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.A, 6.NS.C.7.A, 6.NS.C.7.B, 6.NS.C.7.D</t>
-        </is>
-      </c>
+      <c r="E41" s="13" t="inlineStr"/>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -18676,14 +18372,10 @@
           <t>9.2.3.7, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
+      <c r="E42" s="13" t="inlineStr"/>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022_hs, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CPM_Standards_Alignment_Master.xlsx
+++ b/viewer/downloads/CPM_Standards_Alignment_Master.xlsx
@@ -2492,7 +2492,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>CC1 11.1.1</t>
+          <t>CC1 11.1.1, CC1 2.2.1, CC1 5.3.1, CC1 5.3.2, CC1 5.3.3, CC1 5.3.4</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2893,12 +2893,12 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>CC1 11.1.1</t>
+          <t>CC1 11.1.1, CC1 2.2.1, CC1 5.3.1, CC1 5.3.2, CC1 5.3.3, CC1 5.3.4</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>CC1 10.1.3</t>
+          <t>CC1 10.1.3, CC1 2.2.1, CC1 5.3.1, CC1 5.3.2, CC1 5.3.3, CC1 5.3.4</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>CC1 10.1.3, CC1 8.1.4, CC1 9.1.1, CC1 9.2.2</t>
+          <t>CC1 10.1.3, CC1 2.2.1, CC1 5.3.1, CC1 5.3.2, CC1 5.3.3, CC1 5.3.4, CC1 8.1.4, CC1 9.1.1, CC1 9.2.2</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>CC1 1.1.2, CC1 2.1.1, CC1 6.3.1</t>
+          <t>CC1 1.1.2, CC1 2.1.1, CC1 2.2.1, CC1 5.3.1, CC1 5.3.2, CC1 5.3.3, CC1 5.3.4, CC1 6.3.1</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>CC1 10.3.2</t>
+          <t>CC1 10.3.2, CC1 2.2.1, CC1 5.3.1, CC1 5.3.2, CC1 5.3.3, CC1 5.3.4</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>CC1 10.4.2</t>
+          <t>CC1 10.4.2, CC1 2.2.1, CC1 5.3.1, CC1 5.3.2, CC1 5.3.3, CC1 5.3.4</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>CC1 3.2.4</t>
+          <t>CC1 2.2.1, CC1 3.2.4, CC1 5.3.1, CC1 5.3.2, CC1 5.3.3, CC1 5.3.4</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3184,17 +3184,17 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>CC1 10.1.3, CC1 9.1.1</t>
+          <t>CC1 10.1.3, CC1 2.3.1, CC1 2.3.2, CC1 2.3.4, CC1 4.1.2, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 6.1.1, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.1.2, CC1 7.1.3, CC1 7.2.4, CC1 9.1.1, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3221,17 +3221,17 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>CC1 11.2.2, CC1 3.1.2, CC1 3.1.3, CC1 6.2.1, CC1 7.1.1</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 11.2.2, CC1 2.3.1, CC1 2.3.2, CC1 2.3.3, CC1 2.3.4, CC1 3.1.2, CC1 3.1.3, CC1 3.1.4, CC1 4.1.2, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 6.2.1, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.1.1, CC1 7.1.2, CC1 7.1.3, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4, CC1 9.2.3, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3258,17 +3258,17 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>CC1 3.1.6, CC1 3.2.1, CC1 3.2.2, CC1 3.2.4</t>
+          <t>CC1 3.1.6, CC1 3.2.1, CC1 3.2.2, CC1 3.2.4, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 7.1.2, CC1 7.1.3, CC1 7.2.4, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>CC1 3.2.2, CC1 3.2.3</t>
+          <t>CC1 2.3.1, CC1 2.3.2, CC1 2.3.4, CC1 3.2.2, CC1 3.2.3, CC1 4.1.2, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 6.1.1, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.1.2, CC1 7.1.3, CC1 7.2.4, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>CC1 1.2.4</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 1.2.4, CC1 2.3.3, CC1 3.1.4, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>CC1 2.2.3, CC1 3.1.1, CC1 3.2.2</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 2.2.3, CC1 2.3.3, CC1 3.1.1, CC1 3.1.4, CC1 3.2.2, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3406,17 +3406,17 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>CC1 3.2.3, CC1 3.2.4</t>
+          <t>CC1 3.2.3, CC1 3.2.4, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 7.1.2, CC1 7.1.3, CC1 7.2.4, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>CC1 6.1.4, CC1 8.1.2, CC1 9.2.1, CC1 9.2.2</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 2.3.3, CC1 3.1.4, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 6.1.4, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4, CC1 8.1.2, CC1 9.2.1, CC1 9.2.2</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>CC1 8.1.2, CC1 8.1.4, CC1 9.2.1, CC1 9.2.4</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 2.3.3, CC1 3.1.4, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4, CC1 8.1.2, CC1 8.1.4, CC1 9.2.1, CC1 9.2.4</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>CC1 8.1.1, CC1 8.2.1, CC1 9.1.1, CC1 9.1.2, CC1 9.2.1, CC1 9.2.4</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 2.3.1, CC1 2.3.2, CC1 2.3.3, CC1 2.3.4, CC1 3.1.4, CC1 4.1.2, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4, CC1 8.1.1, CC1 8.2.1, CC1 9.1.1, CC1 9.1.2, CC1 9.2.1, CC1 9.2.4</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>CC1 2.2.2, CC1 8.2.1, CC1 9.3.2, CC1 9.3.3</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 2.2.2, CC1 2.3.1, CC1 2.3.2, CC1 2.3.3, CC1 2.3.4, CC1 3.1.4, CC1 4.1.2, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.1.2, CC1 7.1.3, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4, CC1 8.2.1, CC1 9.3.2, CC1 9.3.3, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3591,17 +3591,17 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>CC1 3.1.3, CC1 3.1.5</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 2.3.1, CC1 2.3.2, CC1 2.3.3, CC1 2.3.4, CC1 3.1.3, CC1 3.1.4, CC1 3.1.5, CC1 4.1.2, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.1.2, CC1 7.1.3, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4, CC1 9.2.3, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3628,17 +3628,17 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>CC1 10.1.3, CC1 5.1.1, CC1 5.1.3, CC1 9.3.1</t>
+          <t>CC1 10.1.3, CC1 2.3.1, CC1 2.3.2, CC1 2.3.4, CC1 4.1.2, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 5.1.1, CC1 5.1.3, CC1 6.1.1, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.1.2, CC1 7.1.3, CC1 7.2.4, CC1 9.3.1, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>CC1 10.1.3, CC1 5.1.1, CC1 5.1.3, CC1 9.3.1</t>
+          <t>CC1 10.1.3, CC1 2.3.1, CC1 2.3.2, CC1 2.3.4, CC1 4.1.2, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 5.1.1, CC1 5.1.3, CC1 6.1.1, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.1.2, CC1 7.1.3, CC1 7.2.4, CC1 9.3.1, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3702,17 +3702,17 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>CC1 3.1.6, CC1 5.2.1</t>
+          <t>CC1 3.1.6, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 5.2.1, CC1 7.1.2, CC1 7.1.3, CC1 7.2.4, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3739,17 +3739,17 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>CC1</t>
+          <t>CC1, CC2</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>CC1 11.2.2, CC1 3.1.2, CC1 6.2.1</t>
+          <t>CC1 1.2.1, CC1 1.2.2, CC1 1.2.3, CC1 11.2.2, CC1 2.3.1, CC1 2.3.2, CC1 2.3.3, CC1 2.3.4, CC1 3.1.2, CC1 3.1.4, CC1 4.1.2, CC1 4.2.1, CC1 4.2.2, CC1 4.2.3, CC1 4.2.4, CC1 5.1.2, CC1 5.1.4, CC1 5.2.2, CC1 6.1.1, CC1 6.1.2, CC1 6.1.3, CC1 6.2.1, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 7.1.2, CC1 7.1.3, CC1 7.2.1, CC1 7.2.2, CC1 7.2.3, CC1 7.2.4, CC2 1.2.4</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>CC1 10.1.3, CC1 5.1.1, CC1 5.1.3, CC1 9.3.1, CC1 9.3.2</t>
+          <t>CC1 10.1.3, CC1 2.3.1, CC1 2.3.2, CC1 2.3.4, CC1 4.1.2, CC1 5.1.1, CC1 5.1.3, CC1 6.1.1, CC1 6.2.2, CC1 6.2.3, CC1 6.2.4, CC1 6.2.5, CC1 9.3.1, CC1 9.3.2</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>CC2 8.2.1, CC2 9.2.1</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 5.2.1, CC2 8.1.2, CC2 8.2.1, CC2 9.2.1</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>CC2 11.2.3, CC2 8.2.1, CC2 8.2.2, CC2 9.2.1</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 11.2.3, CC2 5.2.1, CC2 8.1.2, CC2 8.2.1, CC2 8.2.2, CC2 9.2.1</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>CC2 11.2.3, CC2 8.2.1, CC2 8.2.2, CC2 9.2.1</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 11.2.3, CC2 5.2.1, CC2 8.1.2, CC2 8.2.1, CC2 8.2.2, CC2 9.2.1</t>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -3991,12 +3991,12 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>CC2 9.3.1 CL</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 5.2.1, CC2 8.1.2, CC2 9.3.1 CL</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>CC2 10.1.1, CC2 9.3.1 CL</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 10.1.1, CC2 5.2.1, CC2 8.1.2, CC2 9.3.1 CL</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4065,12 +4065,12 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>CC2 11.2.3, CC2 8.2.1, CC2 8.2.2</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 11.2.3, CC2 5.2.1, CC2 8.1.2, CC2 8.2.1, CC2 8.2.2</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -4102,12 +4102,12 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>CC2 1.2.1, CC2 1.2.2, CC2 2.1.1, CC2 2.1.2</t>
+          <t>CC2 1.1.2, CC2 1.2.1, CC2 1.2.2, CC2 1.2.3, CC2 1.2.5, CC2 2.1.1, CC2 2.1.2, CC2 5.2.1, CC2 8.1.2</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>CC2 1.2.1, CC2 1.2.2, CC2 2.1.1, CC2 2.1.2</t>
+          <t>CC2 1.1.2, CC2 1.2.1, CC2 1.2.2, CC2 1.2.3, CC2 1.2.5, CC2 2.1.1, CC2 2.1.2, CC2 5.2.1, CC2 8.1.2</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4176,12 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>CC2 1.2.7, CC2 1.2.8, CC2 5.2.3, CC2 5.2.6</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 1.2.7, CC2 1.2.8, CC2 5.2.1, CC2 5.2.3, CC2 5.2.6, CC2 8.1.2</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4213,12 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>CC2 5.2.4, CC2 5.2.5</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 5.2.1, CC2 5.2.4, CC2 5.2.5, CC2 8.1.2</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4250,12 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>CC2 5.2.2</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 5.2.1, CC2 5.2.2, CC2 8.1.2</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4287,12 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>CC2 5.2.2, CC2 5.2.4, CC2 5.2.5</t>
+          <t>CC2 1.1.2, CC2 1.2.3, CC2 1.2.5, CC2 5.2.1, CC2 5.2.2, CC2 5.2.4, CC2 5.2.5, CC2 8.1.2</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -4319,17 +4319,17 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>CC2 10.2.1</t>
+          <t>CC2 1.1.4, CC2 10.2.1, CC2 2.3.1, CC2 2.3.2, CC2 9.1.1, CC2 9.1.2, CC2 9.1.3, CC2 9.2.2, CC2 9.2.3, CC2 9.2.4, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4356,17 +4356,17 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>CC2 10.2.1</t>
+          <t>CC2 1.1.4, CC2 10.2.1, CC2 2.3.1, CC2 2.3.2, CC2 9.1.1, CC2 9.1.2, CC2 9.1.3, CC2 9.2.2, CC2 9.2.3, CC2 9.2.4, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4393,17 +4393,17 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>CC2 10.2.1</t>
+          <t>CC2 1.1.4, CC2 10.2.1, CC2 2.3.1, CC2 2.3.2, CC2 9.1.1, CC2 9.1.2, CC2 9.1.3, CC2 9.2.2, CC2 9.2.3, CC2 9.2.4, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4430,17 +4430,17 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>CC2 10.2.1, CC2 10.3.3</t>
+          <t>CC2 1.1.4, CC2 10.2.1, CC2 10.3.3, CC2 2.3.1, CC2 2.3.2, CC2 9.1.1, CC2 9.1.2, CC2 9.1.3, CC2 9.2.2, CC2 9.2.3, CC2 9.2.4, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4467,17 +4467,17 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>CC2 6.1.1, CC2 6.1.3, CC2 6.2.3</t>
+          <t>CC2 1.1.4, CC2 2.3.1, CC2 2.3.2, CC2 6.1.1, CC2 6.1.3, CC2 6.2.3, CC2 9.1.1, CC2 9.1.2, CC2 9.1.3, CC2 9.2.2, CC2 9.2.3, CC2 9.2.4, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4504,17 +4504,17 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>CC2 4.1.1, CC2 4.1.2</t>
+          <t>CC2 1.1.4, CC2 2.3.1, CC2 2.3.2, CC2 4.1.1, CC2 4.1.2, CC2 9.1.1, CC2 9.1.2, CC2 9.1.3, CC2 9.2.2, CC2 9.2.3, CC2 9.2.4, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4541,17 +4541,17 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>CC2 4.4.1</t>
+          <t>CC2 1.1.4, CC2 2.3.1, CC2 2.3.2, CC2 4.4.1, CC2 9.1.1, CC2 9.1.2, CC2 9.1.3, CC2 9.2.2, CC2 9.2.3, CC2 9.2.4, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4578,17 +4578,17 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>CC2 4.1.1, CC2 4.1.2, CC2 4.4.1</t>
+          <t>CC2 1.1.4, CC2 2.3.1, CC2 2.3.2, CC2 4.1.1, CC2 4.1.2, CC2 4.4.1, CC2 9.1.1, CC2 9.1.2, CC2 9.1.3, CC2 9.2.2, CC2 9.2.3, CC2 9.2.4, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4615,17 +4615,17 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>CC2 2.1.1, CC2 2.1.2</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 1.2.6, CC2 2.1.1, CC2 2.1.2, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.2.2, CC2 3.2.4, CC2 3.3.2, CC2 7.1.3, CC2 7.1.5, CC2 7.1.6, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>CC2 2.2.2, CC2 2.2.3, CC2 2.2.4</t>
+          <t>CC2 1.1.5, CC2 2.2.2, CC2 2.2.3, CC2 2.2.4, CC2 2.2.5, CC2 2.2.6, CC2 3.2.2, CC2 3.2.4, CC2 3.3.2, CC2 7.1.3</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4689,17 +4689,17 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>CC2 7.1.1, CC2 7.1.4</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 1.2.6, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.2.2, CC2 3.2.4, CC2 3.3.2, CC2 7.1.1, CC2 7.1.3, CC2 7.1.4, CC2 7.1.5, CC2 7.1.6, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4726,17 +4726,17 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>CC2 3.2.1, CC2 3.2.3</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 1.2.6, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.2.1, CC2 3.2.2, CC2 3.2.3, CC2 3.2.4, CC2 3.3.2, CC2 7.1.3, CC2 7.1.5, CC2 7.1.6, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4763,17 +4763,17 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>CC2 2.2.1, CC2 2.2.3, CC2 3.2.1, CC2 3.2.5, CC2 5.1.1, CC2 5.1.2</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 1.2.6, CC2 2.2.1, CC2 2.2.3, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.2.1, CC2 3.2.2, CC2 3.2.4, CC2 3.2.5, CC2 3.3.2, CC2 5.1.1, CC2 5.1.2, CC2 7.1.3, CC2 7.1.5, CC2 7.1.6, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4800,17 +4800,17 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>CC2 2.2.2, CC2 2.2.3, CC2 3.1.1, CC2 3.3.3</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 1.2.6, CC2 2.2.2, CC2 2.2.3, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.1.1, CC2 3.2.2, CC2 3.2.4, CC2 3.3.2, CC2 3.3.3, CC2 4.3.2, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.1.2, CC2 6.1.4, CC2 6.2.1, CC2 6.2.2, CC2 6.2.4, CC2 6.2.5, CC2 7.1.3, CC2 7.1.5, CC2 7.1.6, CC2 7.1.7, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4837,17 +4837,17 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>CC2 4.1.1, CC2 4.2.3, CC2 4.4.1</t>
+          <t>CC2 1.1.4, CC2 1.2.6, CC2 2.3.1, CC2 2.3.2, CC2 4.1.1, CC2 4.2.3, CC2 4.4.1, CC2 7.1.5, CC2 7.1.6, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4874,17 +4874,17 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>CC2 4.3.1, CC2 4.3.3</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 1.2.6, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.2.2, CC2 3.2.4, CC2 3.3.2, CC2 4.3.1, CC2 4.3.2, CC2 4.3.3, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.1.2, CC2 6.1.4, CC2 6.2.1, CC2 6.2.2, CC2 6.2.4, CC2 6.2.5, CC2 7.1.3, CC2 7.1.5, CC2 7.1.6, CC2 7.1.7, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4911,17 +4911,17 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>CC2 7.1.4, CC2 7.2.1, CC2 8.1.1</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 1.2.6, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.2.2, CC2 3.2.4, CC2 3.3.2, CC2 4.3.2, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.1.2, CC2 6.1.4, CC2 6.2.1, CC2 6.2.2, CC2 6.2.4, CC2 6.2.5, CC2 7.1.3, CC2 7.1.4, CC2 7.1.5, CC2 7.1.6, CC2 7.1.7, CC2 7.1.8, CC2 7.2.1, CC2 7.2.2, CC2 8.1.1, CC3 1.2.2, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>CC2 3.1.2, CC2 3.2.1</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 1.2.6, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.1.2, CC2 3.2.1, CC2 3.2.2, CC2 3.2.4, CC2 3.3.2, CC2 4.3.2, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.1.2, CC2 6.1.4, CC2 6.2.1, CC2 6.2.2, CC2 6.2.4, CC2 6.2.5, CC2 7.1.3, CC2 7.1.5, CC2 7.1.6, CC2 7.1.7, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -4985,17 +4985,17 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>CC2 5.1.1, CC2 5.1.2, CC2 8.1.1, CC2 8.2.2</t>
+          <t>CC2 1.1.4, CC2 1.1.5, CC2 2.2.5, CC2 2.2.6, CC2 2.3.1, CC2 2.3.2, CC2 3.2.2, CC2 3.2.4, CC2 3.3.2, CC2 4.3.2, CC2 5.1.1, CC2 5.1.2, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.1.2, CC2 6.1.4, CC2 6.2.1, CC2 6.2.2, CC2 6.2.4, CC2 6.2.5, CC2 7.1.3, CC2 7.1.7, CC2 7.1.8, CC2 7.2.2, CC2 8.1.1, CC2 8.2.2, CC3 1.2.2, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5022,17 +5022,17 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>CC2 3.2.5, CC2 3.3.1, CC2 3.3.3, CC2 8.1.1</t>
+          <t>CC2 3.2.5, CC2 3.3.1, CC2 3.3.3, CC2 4.3.2, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.1.2, CC2 6.1.4, CC2 6.2.1, CC2 6.2.2, CC2 6.2.4, CC2 6.2.5, CC2 7.1.7, CC2 7.1.8, CC2 7.2.2, CC2 8.1.1, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5059,17 +5059,17 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>CC2 4.2.2, CC2 4.2.4</t>
+          <t>CC2 1.1.4, CC2 2.3.1, CC2 2.3.2, CC2 4.2.2, CC2 4.2.4, CC2 4.3.2, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.1.2, CC2 6.1.4, CC2 6.2.1, CC2 6.2.2, CC2 6.2.4, CC2 6.2.5, CC2 7.1.7, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5097,17 +5097,17 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>CC2 4.2.1, CC2 4.2.4</t>
+          <t>CC2 1.1.4, CC2 2.3.1, CC2 2.3.2, CC2 4.2.1, CC2 4.2.4, CC2 4.3.2, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.1.2, CC2 6.1.4, CC2 6.2.1, CC2 6.2.2, CC2 6.2.4, CC2 6.2.5, CC2 7.1.7, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5134,17 +5134,17 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>CC2</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>CC2 4.2.2, CC2 4.2.4</t>
+          <t>CC2 1.1.4, CC2 2.3.1, CC2 2.3.2, CC2 4.2.2, CC2 4.2.4, CC2 4.3.2, CC2 5.3.1, CC2 5.3.2, CC2 5.3.3, CC2 5.3.4, CC2 5.3.5, CC2 6.2.4, CC2 6.2.5, CC2 7.1.7, CC2 7.1.8, CC2 7.2.2, CC3 1.2.2, CC3 2.1.1, CC3 2.1.3, CC3 2.1.6</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>CC3 1.1.4, CC3 7.1.2, CC3 7.3.2, CC3 7.3.3</t>
+          <t>CC3 1.1.4, CC3 7.1.2, CC3 7.1.3, CC3 7.3.2, CC3 7.3.3</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>CC3 7.1.1, CC3 7.1.2</t>
+          <t>CC3 7.1.1, CC3 7.1.2, CC3 7.1.3</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>CC3 7.3.1, CC3 7.3.2</t>
+          <t>CC3 7.1.3, CC3 7.3.1, CC3 7.3.2</t>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>CC3 7.1.2, CC3 7.3.2</t>
+          <t>CC3 7.1.2, CC3 7.1.3, CC3 7.3.2</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>CC3 1.1.4, CC3 7.3.2</t>
+          <t>CC3 1.1.4, CC3 7.1.3, CC3 7.3.2</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5423,12 +5423,12 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>CC3 1.1.4, CC3 7.1.2, CC3 7.3.2</t>
+          <t>CC3 1.1.4, CC3 7.1.2, CC3 7.1.3, CC3 7.3.2</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>CC3 9.1.1, CC3 9.1.2, CC3 9.1.3</t>
+          <t>CC3 10.1.4, CC3 10.1.5, CC3 6.1.1, CC3 6.1.2, CC3 6.1.3, CC3 6.1.4, CC3 6.2.3, CC3 6.2.4, CC3 6.2.5, CC3 6.2.6, CC3 9.1.1, CC3 9.1.2, CC3 9.1.3, CC3 9.2.1, CC3 9.2.2, CC3 9.2.5, CC3 9.2.6</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>CC3 9.1.1, CC3 9.1.2</t>
+          <t>CC3 10.1.4, CC3 10.1.5, CC3 6.1.1, CC3 6.1.2, CC3 6.1.3, CC3 6.1.4, CC3 6.2.3, CC3 6.2.4, CC3 6.2.5, CC3 6.2.6, CC3 9.1.1, CC3 9.1.2, CC3 9.2.1, CC3 9.2.2, CC3 9.2.5, CC3 9.2.6</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>CC3 9.1.1</t>
+          <t>CC3 10.1.4, CC3 10.1.5, CC3 6.1.1, CC3 6.1.2, CC3 6.1.3, CC3 6.1.4, CC3 6.2.3, CC3 6.2.4, CC3 6.2.5, CC3 6.2.6, CC3 9.1.1, CC3 9.2.1, CC3 9.2.2, CC3 9.2.5, CC3 9.2.6</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5571,12 +5571,12 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>CC3 3.1.2, CC3 3.1.6, CC3 7.2.1, CC3 8.1.1, CC3 8.1.3</t>
+          <t>CC3 10.1.4, CC3 10.1.5, CC3 3.1.2, CC3 3.1.6, CC3 6.1.1, CC3 6.1.2, CC3 6.1.3, CC3 6.1.4, CC3 6.2.3, CC3 6.2.4, CC3 6.2.5, CC3 6.2.6, CC3 7.2.1, CC3 8.1.1, CC3 8.1.3, CC3 9.2.1, CC3 9.2.2, CC3 9.2.5, CC3 9.2.6</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>CC3 7.2.1</t>
+          <t>CC3 10.1.4, CC3 10.1.5, CC3 6.1.1, CC3 6.1.2, CC3 6.1.3, CC3 6.1.4, CC3 6.2.3, CC3 6.2.4, CC3 6.2.5, CC3 6.2.6, CC3 7.2.1, CC3 9.2.1, CC3 9.2.2, CC3 9.2.5, CC3 9.2.6</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5645,12 +5645,12 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>CC3 5.2.4</t>
+          <t>CC3 10.1.4, CC3 10.1.5, CC3 5.2.4, CC3 6.1.1, CC3 6.1.2, CC3 6.1.3, CC3 6.1.4, CC3 6.2.3, CC3 6.2.4, CC3 6.2.5, CC3 6.2.6, CC3 9.2.1, CC3 9.2.2, CC3 9.2.5, CC3 9.2.6</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5682,12 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>CC3 9.1.4</t>
+          <t>CC3 1.1.3, CC3 1.2.1, CC3 4.1.4, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 8.2.2, CC3 9.1.4, CC3 9.2.3, CC3 9.2.4</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5714,17 +5714,17 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>CC3 9.1.3, CC3 9.1.4</t>
+          <t>CC2 1.1.3, CC3 1.1.3, CC3 1.2.1, CC3 3.2.3, CC3 4.1.4, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 8.2.2, CC3 9.1.3, CC3 9.1.4, CC3 9.2.3, CC3 9.2.4</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5751,17 +5751,17 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>CC3 8.2.1, CC3 8.2.3</t>
+          <t>CC2 1.1.3, CC3 1.1.3, CC3 1.2.1, CC3 3.2.3, CC3 4.1.4, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 8.2.1, CC3 8.2.2, CC3 8.2.3, CC3 9.2.3, CC3 9.2.4</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5793,12 +5793,12 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>CC3 8.2.1, CC3 8.2.4</t>
+          <t>CC3 8.2.1, CC3 8.2.2, CC3 8.2.4</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>CC3 8.2.1, CC3 8.2.4</t>
+          <t>CC3 8.2.1, CC3 8.2.2, CC3 8.2.4</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5862,17 +5862,17 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>CC3 8.1.1, CC3 8.1.2, CC3 8.1.3</t>
+          <t>CC2 1.1.3, CC3 1.1.3, CC3 1.2.1, CC3 3.2.3, CC3 4.1.4, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 8.1.1, CC3 8.1.2, CC3 8.1.3</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5899,17 +5899,17 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>CC3 8.1.1, CC3 8.1.2, CC3 8.1.3</t>
+          <t>CC2 1.1.3, CC3 1.1.3, CC3 1.2.1, CC3 3.2.3, CC3 4.1.4, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 8.1.1, CC3 8.1.2, CC3 8.1.3</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>CC3 7.2.1</t>
+          <t>CC3 1.1.2, CC3 3.1.4, CC3 4.1.2, CC3 4.1.6, CC3 7.2.1</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -5973,17 +5973,17 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>CC3 2.1.2, CC3 2.1.5, CC3 2.1.7, CC3 3.2.5</t>
+          <t>CC2 1.1.3, CC3 1.1.3, CC3 1.2.1, CC3 2.1.2, CC3 2.1.5, CC3 2.1.7, CC3 3.2.3, CC3 3.2.5, CC3 4.1.4, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6010,17 +6010,17 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>CC3 2.1.4</t>
+          <t>CC2 1.1.3, CC3 1.1.3, CC3 1.2.1, CC3 2.1.4, CC3 3.2.3, CC3 4.1.4, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 9.2.3, CC3 9.2.4</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6047,17 +6047,17 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>CC3 2.1.8, CC3 2.1.9, CC3 3.2.1, CC3 3.2.2, CC3 3.2.5, CC3 5.1.1, CC3 5.1.2</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 2.1.8, CC3 2.1.9, CC3 3.1.4, CC3 3.2.1, CC3 3.2.2, CC3 3.2.3, CC3 3.2.5, CC3 4.1.2, CC3 4.1.4, CC3 4.1.6, CC3 5.1.1, CC3 5.1.2, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6084,17 +6084,17 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>CC3 9.1.3, CC3 9.1.4</t>
+          <t>CC2 1.1.3, CC3 1.1.3, CC3 1.2.1, CC3 3.2.3, CC3 4.1.4, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 8.2.2, CC3 9.1.3, CC3 9.1.4</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6126,12 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>CC3 4.1.3, CC3 4.1.5, CC3 7.2.1</t>
+          <t>CC3 1.1.2, CC3 3.1.4, CC3 4.1.2, CC3 4.1.3, CC3 4.1.5, CC3 4.1.6, CC3 7.2.1</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6158,17 +6158,17 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>CC3 4.1.3, CC3 4.1.5, CC3 7.2.1</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 3.1.4, CC3 3.2.3, CC3 4.1.2, CC3 4.1.3, CC3 4.1.4, CC3 4.1.5, CC3 4.1.6, CC3 5.2.2, CC3 5.2.3, CC3 7.2.1, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6195,17 +6195,17 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>CC3 10.1.1, CC3 10.1.2</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 10.1.1, CC3 10.1.2, CC3 3.1.4, CC3 3.2.3, CC3 4.1.2, CC3 4.1.4, CC3 4.1.6, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 9.2.3, CC3 9.2.4</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6232,17 +6232,17 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>CC3 10.1.3</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 10.1.3, CC3 3.1.4, CC3 3.2.3, CC3 4.1.2, CC3 4.1.4, CC3 4.1.6, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 9.2.3, CC3 9.2.4</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6269,17 +6269,17 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>CC3 10.2.1, CC3 10.4.2, CC3 5.2.1, CC3 5.2.4</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 10.2.1, CC3 10.4.2, CC3 3.1.4, CC3 3.2.3, CC3 4.1.2, CC3 4.1.4, CC3 4.1.6, CC3 5.2.1, CC3 5.2.2, CC3 5.2.3, CC3 5.2.4, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>CC3 3.1.2, CC3 3.1.5, CC3 3.2.4, CC3 4.1.1, CC3 4.1.7, CC3 7.2.1, CC3 7.2.5</t>
+          <t>CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 3.1.2, CC3 3.1.4, CC3 3.1.5, CC3 3.2.4, CC3 4.1.1, CC3 4.1.2, CC3 4.1.4, CC3 4.1.6, CC3 4.1.7, CC3 7.2.1, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 7.2.5</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6343,17 +6343,17 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>CC3 3.1.1, CC3 3.1.3, CC3 4.1.1, CC3 4.1.3, CC3 4.1.7</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 3.1.1, CC3 3.1.3, CC3 3.1.4, CC3 3.2.3, CC3 4.1.1, CC3 4.1.2, CC3 4.1.3, CC3 4.1.4, CC3 4.1.6, CC3 4.1.7, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6380,17 +6380,17 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>CC3 3.1.2, CC3 3.1.6, CC3 7.2.1, CC3 8.1.1, CC3 8.1.3, CC3 8.3.1</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 3.1.2, CC3 3.1.4, CC3 3.1.6, CC3 3.2.3, CC3 4.1.2, CC3 4.1.4, CC3 4.1.6, CC3 5.2.2, CC3 5.2.3, CC3 7.2.1, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 8.1.1, CC3 8.1.3, CC3 8.2.2, CC3 8.3.1, CC3 9.2.3, CC3 9.2.4</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6417,17 +6417,17 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>CC3 3.1.2, CC3 3.1.7, CC3 4.1.1, CC3 4.1.7</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 3.1.2, CC3 3.1.4, CC3 3.1.7, CC3 3.2.3, CC3 4.1.1, CC3 4.1.2, CC3 4.1.4, CC3 4.1.6, CC3 4.1.7, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6454,17 +6454,17 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>CC3 4.1.3</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 3.1.4, CC3 3.2.3, CC3 4.1.2, CC3 4.1.3, CC3 4.1.4, CC3 4.1.6, CC3 5.2.2, CC3 5.2.3, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6497,12 +6497,12 @@
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>CC3 3.1.1, CC3 3.1.7, CC3 4.1.1, CC3 4.1.7, CC3 7.2.1, CC3 8.3.1</t>
+          <t>CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 3.1.1, CC3 3.1.4, CC3 3.1.7, CC3 4.1.1, CC3 4.1.2, CC3 4.1.4, CC3 4.1.6, CC3 4.1.7, CC3 7.2.1, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4, CC3 8.3.1</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>CC3 6.2.1, CC3 6.2.2</t>
+          <t>CC3 1.1.2, CC3 3.1.4, CC3 4.1.2, CC3 4.1.6, CC3 6.2.1, CC3 6.2.2</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>CC3 6.2.1, CC3 6.2.2</t>
+          <t>CC3 1.1.2, CC3 3.1.4, CC3 4.1.2, CC3 4.1.6, CC3 6.2.1, CC3 6.2.2</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -6603,17 +6603,17 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>CC3</t>
+          <t>CC2, CC3</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>CC3 6.2.1, CC3 6.2.2</t>
+          <t>CC2 1.1.3, CC3 1.1.2, CC3 1.1.3, CC3 1.2.1, CC3 3.2.3, CC3 4.1.4, CC3 5.2.2, CC3 5.2.3, CC3 6.2.1, CC3 6.2.2, CC3 7.2.2, CC3 7.2.3, CC3 7.2.4</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,11 @@
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr"/>
-      <c r="D8" s="13" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
           <t>6.NS.B.4</t>
@@ -9733,7 +9737,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9751,11 @@
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr"/>
-      <c r="D9" s="13" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
           <t>6.NS.B.4</t>
@@ -9755,7 +9763,7 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9781,11 @@
           <t>Number Sense</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
           <t>6.NS.B.4</t>
@@ -9781,7 +9793,7 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9913,11 @@
           <t>Area of Polygons</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr"/>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>6.2.3.1, 6.2.3.2, 6.2.3.3, 6.2.3.4, 6.2.3.5, 6.2.4.1, 6.2.4.2, 6.2.4.3</t>
+        </is>
+      </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
           <t>6.G.A.1</t>
@@ -9909,7 +9925,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -9987,7 +10003,11 @@
           <t>Multiplying Multi-Digit Numbers</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
           <t>6.EE.A.3, 6.NS.B.2</t>
@@ -9995,7 +10015,7 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10033,11 @@
           <t>Multiplying Multi-Digit Numbers</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr"/>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
           <t>6.EE.A.3</t>
@@ -10021,7 +10045,7 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10063,11 @@
           <t>Defining Greatest Common Factor</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
           <t>6.NS.B.4</t>
@@ -10047,7 +10075,7 @@
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10093,11 @@
           <t>Understanding the Distributive Property</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr"/>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
           <t>6.EE.A.3</t>
@@ -10073,7 +10105,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10225,11 @@
           <t>Representing Portions in Multiple Ways</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
           <t>6.NS.B.3</t>
@@ -10201,7 +10237,7 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10477,11 @@
           <t>Writing Equivalent Expressions</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr"/>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
           <t>6.EE.A.4, 6.EE.B.6</t>
@@ -10449,7 +10489,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10537,11 @@
           <t>Using Scale Factor for Enlargement</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr"/>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.6, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
           <t>6.RP.A.1</t>
@@ -10505,7 +10549,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10567,11 @@
           <t>Using Scale Factor for Enlargement and Reduction</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr"/>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.6, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
           <t>6.RP.A.1</t>
@@ -10531,7 +10579,7 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10597,11 @@
           <t>Using Ratios to Compare Similar Figures</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr"/>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.6, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
           <t>6.RP.A.1</t>
@@ -10557,7 +10609,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10627,11 @@
           <t>Using Ratios that Apply to Different Contexts</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr"/>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.6, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
           <t>6.RP.A.1</t>
@@ -10583,7 +10639,7 @@
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10643,9 +10699,17 @@
           <t>Representing Fraction Multiplication</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr"/>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="13" t="inlineStr"/>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
@@ -10691,7 +10755,11 @@
           <t>Multiplying Mixed Numbers</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr"/>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
           <t>Review skills needed for 6.NS.1</t>
@@ -10699,7 +10767,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10815,11 @@
           <t>Fraction Multiplication Number Sense</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr"/>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
           <t>Review skills needed for 6.NS.1</t>
@@ -10755,7 +10827,7 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10773,7 +10845,11 @@
           <t>Decompose shapes into rectangles to find area</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr"/>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>6.2.3.1, 6.2.3.2, 6.2.3.3, 6.2.3.4, 6.2.3.5, 6.2.4.1, 6.2.4.2, 6.2.4.3</t>
+        </is>
+      </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
           <t>6.G.1</t>
@@ -10781,7 +10857,7 @@
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10875,11 @@
           <t>Area of Parallelogram</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr"/>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>6.2.3.1, 6.2.3.2, 6.2.3.3, 6.2.3.4, 6.2.3.5, 6.2.4.1, 6.2.4.2, 6.2.4.3</t>
+        </is>
+      </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
           <t>6.G.1</t>
@@ -10807,7 +10887,7 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10825,7 +10905,11 @@
           <t>Area of Triangles</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr"/>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>6.2.3.1, 6.2.3.2, 6.2.3.3, 6.2.3.4, 6.2.3.5, 6.2.4.1, 6.2.4.2, 6.2.4.3</t>
+        </is>
+      </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
           <t>6.G.1</t>
@@ -10833,7 +10917,7 @@
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10935,11 @@
           <t>Area of Trapezoids</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr"/>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>6.2.3.1, 6.2.3.2, 6.2.3.3, 6.2.3.4, 6.2.3.5, 6.2.4.1, 6.2.4.2, 6.2.4.3</t>
+        </is>
+      </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
           <t>6.G.1</t>
@@ -10859,7 +10947,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -10889,9 +10977,17 @@
           <t>Quotients can be expressed as addition expressions, fractions greater than 1, and mixed numbers</t>
         </is>
       </c>
-      <c r="D53" s="13" t="inlineStr"/>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E53" s="13" t="inlineStr"/>
-      <c r="F53" s="13" t="inlineStr"/>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
@@ -10907,9 +11003,17 @@
           <t>Consider meanings of numbers in a division problem as what they represent changes</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr"/>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E54" s="13" t="inlineStr"/>
-      <c r="F54" s="13" t="inlineStr"/>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n">
@@ -10925,9 +11029,17 @@
           <t>Dividing by unit fractions is equivalent to multiplying by the denominator</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr"/>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E55" s="13" t="inlineStr"/>
-      <c r="F55" s="13" t="inlineStr"/>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
@@ -10995,9 +11107,17 @@
           <t>Algebra Tiles</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr"/>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E58" s="13" t="inlineStr"/>
-      <c r="F58" s="13" t="inlineStr"/>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
@@ -11013,9 +11133,17 @@
           <t>Algebra Tiles</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr"/>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E59" s="13" t="inlineStr"/>
-      <c r="F59" s="13" t="inlineStr"/>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
@@ -11031,9 +11159,17 @@
           <t>Combining Like Terms</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr"/>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E60" s="13" t="inlineStr"/>
-      <c r="F60" s="13" t="inlineStr"/>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n">
@@ -11049,9 +11185,17 @@
           <t>Evaluate expressions</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.3, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.6, 6.3.7.1</t>
+        </is>
+      </c>
       <c r="E61" s="13" t="inlineStr"/>
-      <c r="F61" s="13" t="inlineStr"/>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="n">
@@ -11127,9 +11271,17 @@
           <t>Compare using tables and graphs</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr"/>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.6, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E65" s="13" t="inlineStr"/>
-      <c r="F65" s="13" t="inlineStr"/>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="n">
@@ -11145,9 +11297,17 @@
           <t>Compare using unit rates</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr"/>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.6, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E66" s="13" t="inlineStr"/>
-      <c r="F66" s="13" t="inlineStr"/>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="n">
@@ -11185,9 +11345,17 @@
           <t>Model fraction division</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr"/>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E68" s="13" t="inlineStr"/>
-      <c r="F68" s="13" t="inlineStr"/>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="n">
@@ -11203,9 +11371,17 @@
           <t>Alternate Strategies for fraction division</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr"/>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E69" s="13" t="inlineStr"/>
-      <c r="F69" s="13" t="inlineStr"/>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="n">
@@ -11221,9 +11397,17 @@
           <t>Fraction Division Algorithm</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr"/>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.5.4, 6.3.5.5, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E70" s="13" t="inlineStr"/>
-      <c r="F70" s="13" t="inlineStr"/>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="n">
@@ -11239,9 +11423,17 @@
           <t>Fraction Division as Ratios</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr"/>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.4, 6.3.5.5, 6.3.5.6, 6.3.5.7, 6.3.5.8, 6.3.5.9, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E71" s="13" t="inlineStr"/>
-      <c r="F71" s="13" t="inlineStr"/>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="n">
@@ -11631,9 +11823,17 @@
           <t>Use percent knowledge to calculate discounts and sale prices</t>
         </is>
       </c>
-      <c r="D91" s="13" t="inlineStr"/>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.11, 6.3.6.2</t>
+        </is>
+      </c>
       <c r="E91" s="13" t="inlineStr"/>
-      <c r="F91" s="13" t="inlineStr"/>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>bridged_via_content</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="n">
@@ -11880,7 +12080,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
@@ -11969,7 +12169,11 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr"/>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
           <t>7.SP.8c, 7.SP.C.6, 7.SP.C.8.C</t>
@@ -11977,7 +12181,7 @@
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -11995,7 +12199,11 @@
           <t>Variables and Solutions</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr"/>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
           <t>7.SP.8c, 8.EE.C.7.B</t>
@@ -12003,7 +12211,7 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12229,11 @@
           <t>Proportional Reasoning</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr"/>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4, 7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
           <t>7.RP.A.2, 7.SP.8c</t>
@@ -12029,7 +12241,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12047,7 +12259,11 @@
           <t>Rational numbers and decimals</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr"/>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
           <t>7.NS.A.2.D, 7.SP.8c</t>
@@ -12055,7 +12271,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12349,11 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
           <t>7.SP.7a, 7.SP.8c, 7.SP.C.7.A</t>
@@ -12141,7 +12361,7 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12379,11 @@
           <t>Percent</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.6, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
           <t>6.RP.A.3, 7.SP.8c</t>
@@ -12167,7 +12391,7 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12185,7 +12409,11 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
           <t>7.SP.8c, Prep for 7.SP.C.8.A</t>
@@ -12193,7 +12421,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12211,7 +12439,11 @@
           <t>Fraction Addition</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr"/>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3</t>
+        </is>
+      </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
           <t>5.NF.A.1, 7.SP.8c</t>
@@ -12219,7 +12451,7 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12491,7 +12723,11 @@
           <t>Multiplication of Rational Numbers</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr"/>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
           <t>7.NS.2a, 7.NS.A.2.A, 7.NS.A.2.C, 7.SP.8c</t>
@@ -12499,7 +12735,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12517,7 +12753,11 @@
           <t>Multiplying of Mixed Numbers</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
           <t>7.NS.2a, 7.NS.A.2.C, 7.SP.8c</t>
@@ -12525,7 +12765,7 @@
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12783,11 @@
           <t>Graphing Points on a Coordinate Plane</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4, 7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.RP.A.2.A, 7.RP.A.2.D, 7.SP.8c</t>
@@ -12551,7 +12795,7 @@
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12813,11 @@
           <t>Graphing Points on a Coordinate Plane</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4, 7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.RP.A.2.A, 7.RP.A.2.B</t>
@@ -12577,7 +12825,7 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12946,11 @@
           <t>Adding and Subtracting Integers</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr"/>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
           <t>7.NS.1c, 7.NS.1d, 7.NS.A.1.C, 7.NS.A.1.D, 7.RP.2b</t>
@@ -12706,7 +12958,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12754,7 +13006,11 @@
           <t>Multiplying Decimals</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr"/>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
           <t>7.NS.2a, 7.NS.A.2.A, 7.NS.A.2.C, 7.RP.2b</t>
@@ -12762,7 +13018,7 @@
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -12840,7 +13096,11 @@
           <t>Dividing Decimals</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr"/>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
           <t>7.NS.A.2.C, 7.NS.A.3, 7.RP.2b</t>
@@ -12848,7 +13108,7 @@
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13378,11 @@
           <t>Using the Distributive Property</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr"/>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
           <t>7.EE.A.1, 7.RP.2b</t>
@@ -13126,7 +13390,7 @@
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13268,7 +13532,11 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr"/>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.SP.7a</t>
@@ -13276,7 +13544,7 @@
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13712,11 @@
           <t>Describing Relationships Between Quantities</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr"/>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -13452,7 +13724,7 @@
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13742,11 @@
           <t>Solving Word Problems</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr"/>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -13478,7 +13754,7 @@
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13772,11 @@
           <t>Solving Word Problems</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr"/>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -13504,7 +13784,7 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13802,11 @@
           <t>Solving Word Problems with Variables</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -13530,7 +13814,7 @@
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13832,11 @@
           <t>Solving Word Problems with Variables</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr"/>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -13556,7 +13844,7 @@
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13904,11 @@
           <t>Comparing Expressions with Variables</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr"/>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2</t>
+        </is>
+      </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
           <t>7.EE.4a, 7.EE.4b, 7.RP.2b</t>
@@ -13624,7 +13916,7 @@
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13964,11 @@
           <t>Solve one-variable inequalities</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr"/>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2</t>
+        </is>
+      </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
           <t>7.EE.4b, 7.RP.2b</t>
@@ -13680,7 +13976,7 @@
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13698,7 +13994,11 @@
           <t>Solving Equations</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr"/>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2</t>
+        </is>
+      </c>
       <c r="E68" s="19" t="inlineStr">
         <is>
           <t>7.EE.4a, 7.RP.2b</t>
@@ -13706,7 +14006,7 @@
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13724,7 +14024,11 @@
           <t>Solving Equations and the Distributive Property</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr"/>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2</t>
+        </is>
+      </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
           <t>7.EE.4a, 7.RP.2b</t>
@@ -13732,7 +14036,7 @@
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13780,7 +14084,11 @@
           <t>Writing equations from Word Problems</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr"/>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
           <t>7.EE.3, 7.EE.4a, 7.RP.2b</t>
@@ -13788,7 +14096,7 @@
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13806,7 +14114,11 @@
           <t>Writing and Solving Equations</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr"/>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
           <t>7.EE.3, 7.EE.4a, 7.RP.2b</t>
@@ -13814,7 +14126,7 @@
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -13952,7 +14264,11 @@
           <t>Solving Problems Involving Percents</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr"/>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
           <t>7.NS.3, 7.RP.2b, 7.RP.3, see ebook</t>
@@ -13960,7 +14276,7 @@
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14324,11 @@
           <t>Creating Integer Coefficients</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr"/>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3</t>
+        </is>
+      </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
           <t>7.RP.2b, see ebook</t>
@@ -14016,7 +14336,7 @@
       </c>
       <c r="F80" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14354,11 @@
           <t>Creating Integer Coefficients Efficently</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr"/>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3</t>
+        </is>
+      </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
           <t>7.EE.2, 7.EE.4a, 7.RP.2b, see ebook</t>
@@ -14042,7 +14366,7 @@
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14384,11 @@
           <t>Percent Increase and Decrease</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr"/>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
           <t>7.EE.3, 7.EE.4a, 7.RP.2b, 7.RP.3, see ebook</t>
@@ -14068,7 +14396,7 @@
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14414,11 @@
           <t>Simple Interest</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr"/>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.RP.3, see ebook</t>
@@ -14094,7 +14426,7 @@
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14474,11 @@
           <t>Solving Proportions</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr"/>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.RP.3, see ebook</t>
@@ -14150,7 +14486,7 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14546,11 @@
           <t>Comparing Distributions</t>
         </is>
       </c>
-      <c r="D88" s="13" t="inlineStr"/>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.SP.3, see ebook</t>
@@ -14218,7 +14558,7 @@
       </c>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14412,7 +14752,11 @@
           <t>Circumference, Diameter, and Pi</t>
         </is>
       </c>
-      <c r="D96" s="13" t="inlineStr"/>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E96" s="19" t="inlineStr">
         <is>
           <t>7.2.1, 7.G.4, 7.RP.2b, see ebook</t>
@@ -14420,7 +14764,7 @@
       </c>
       <c r="F96" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14438,7 +14782,11 @@
           <t>area of circles</t>
         </is>
       </c>
-      <c r="D97" s="13" t="inlineStr"/>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
           <t>7.RP.2b, see ebook</t>
@@ -14446,7 +14794,7 @@
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14464,7 +14812,11 @@
           <t>Area of Composite Shapes</t>
         </is>
       </c>
-      <c r="D98" s="13" t="inlineStr"/>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E98" s="19" t="inlineStr">
         <is>
           <t>7.G.4, 7.G.6, 7.RP.2b, see ebook</t>
@@ -14472,7 +14824,7 @@
       </c>
       <c r="F98" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14520,7 +14872,11 @@
           <t>Cross Sections</t>
         </is>
       </c>
-      <c r="D100" s="13" t="inlineStr"/>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E100" s="19" t="inlineStr">
         <is>
           <t>7.2.1, 7.G.3, 7.RP.2b, see ebook</t>
@@ -14528,7 +14884,7 @@
       </c>
       <c r="F100" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14902,11 @@
           <t>Volume of Prsms</t>
         </is>
       </c>
-      <c r="D101" s="13" t="inlineStr"/>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
           <t>7.G.6, 7.RP.2b, see ebook</t>
@@ -14554,7 +14914,7 @@
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14932,11 @@
           <t>Volume of Non-Rectangular Prisms</t>
         </is>
       </c>
-      <c r="D102" s="13" t="inlineStr"/>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E102" s="19" t="inlineStr">
         <is>
           <t>7.G.6, 7.RP.2b, see ebook</t>
@@ -14580,7 +14944,7 @@
       </c>
       <c r="F102" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14850,7 +15214,11 @@
           <t>Pattern Recognition</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr"/>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.8, 8.3.6.3, 8.3.6.5, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.7, 8.3.7.8, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
           <t>MP4, MP8</t>
@@ -14858,7 +15226,7 @@
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_content, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -14877,7 +15245,11 @@
 Linear Graphs</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr"/>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
           <t>8.EE.B.5, 8.F.A.3</t>
@@ -14885,7 +15257,7 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -14934,7 +15306,11 @@
           <t>Proportinal Relationships</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr"/>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
           <t>8.EE.5, 8.F.A.2</t>
@@ -14942,7 +15318,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -14961,7 +15337,11 @@
 Solving Proportions</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4, 7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
           <t>7.RP.A.2.A, 8.EE.7a</t>
@@ -14969,7 +15349,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15380,11 @@
 Simplyfiing Expressions</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
           <t>7.EE.A.1, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
@@ -15008,7 +15392,7 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15057,7 +15441,11 @@
           <t>Simplifying Algebraic Expressions</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
           <t>7.EE.A.1, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
@@ -15065,7 +15453,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15534,11 @@
 Simplifying Aglebraic Expressions</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr"/>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
           <t>7.EE.B.4.B, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
@@ -15154,7 +15546,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15757,11 @@
           <t>Graphing Data</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr"/>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.8, 8.3.6.3, 8.3.6.5, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.7, 8.3.7.8</t>
+        </is>
+      </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
           <t>8.F.1, 8.F.2, 8.F.3, 8.F.4, 8.F.A.1, 8.F.B.4</t>
@@ -15373,7 +15769,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15541,7 +15937,11 @@
           <t>Solving Equations</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr"/>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
           <t>8.EE.7b, 8.EE.C.7.A, 8.EE.C.7.B</t>
@@ -15549,7 +15949,7 @@
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15669,7 +16069,11 @@
           <t>Writing Linear Equations</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr"/>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.8, 8.3.6.3, 8.3.6.5, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.7, 8.3.7.8</t>
+        </is>
+      </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
           <t>8.F.2, 8.F.4, 8.F.A.2, 8.F.B.4</t>
@@ -15677,7 +16081,7 @@
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15725,7 +16129,11 @@
           <t>Writing Linear Equations</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr"/>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
           <t>8.EE.6, 8.EE.B.6, 8.F.2, 8.F.4, 8.F.A.2, 8.F.B.4</t>
@@ -15733,7 +16141,7 @@
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15781,7 +16189,11 @@
           <t>Graphing Linear Equations</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr"/>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.8, 8.3.6.3, 8.3.6.5, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.7, 8.3.7.8</t>
+        </is>
+      </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
           <t>8.F.2, 8.F.4, 8.F.A.3, 8.F.B.4</t>
@@ -15789,7 +16201,7 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15939,7 +16351,11 @@
           <t>Writing Rules from Word Problems</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr"/>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
           <t>8.EE.8c, 8.EE.C.8</t>
@@ -15947,7 +16363,7 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -15965,7 +16381,11 @@
           <t>Solving Systems</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr"/>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
           <t>8.EE.8b, 8.EE.8c, 8.EE.B.8, 8.EE.C.8</t>
@@ -15973,7 +16393,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16453,11 @@
           <t>Rigid Transformations</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr"/>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
           <t>8.G.1a, 8.G.1b, 8.G.1c, 8.G.A.1, 8.G.B.1, 8.G.C.1</t>
@@ -16041,7 +16465,7 @@
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16483,11 @@
           <t>Rigid Transformations</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr"/>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
           <t>8.G.1a, 8.G.1b, 8.G.1c, 8.G.2, 8.G.3, 8.G.4, 8.G.A.1, 8.G.B.1, 8.G.C.1</t>
@@ -16067,7 +16495,7 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16085,7 +16513,11 @@
           <t>Rigid Transformations</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr"/>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
           <t>8.G.1a, 8.G.1b, 8.G.1c, 8.G.2, 8.G.3, 8.G.4, 8.G.A.1, 8.G.B.1, 8.G.C.1</t>
@@ -16093,7 +16525,7 @@
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16111,7 +16543,11 @@
           <t>Rigid Transformations</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr"/>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
           <t>8.G.3</t>
@@ -16119,7 +16555,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16633,11 @@
           <t>Similarity, Congruence, and Scale Factor</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr"/>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
           <t>8.G.1a, 8.G.1b, 8.G.1c, 8.G.2, 8.G.4, 8.G.A.1, 8.G.B.1, 8.G.C.1</t>
@@ -16205,7 +16645,7 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16663,11 @@
           <t>Similar Figures &amp; Transformations</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr"/>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
           <t>8.G.2, 8.G.4</t>
@@ -16231,7 +16675,7 @@
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -16249,7 +16693,11 @@
           <t>Similar Figures</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr"/>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
           <t>8.G.4</t>
@@ -16257,7 +16705,7 @@
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16723,11 @@
           <t>Similar Figures</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr"/>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
           <t>8.G.4</t>
@@ -16283,7 +16735,7 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16825,11 @@
           <t>Scatterplots &amp; Association</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>8.1.1.1, 8.1.1.2, 8.1.1.3, 8.1.1.4, 8.1.1.5, 8.1.1.6</t>
+        </is>
+      </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
           <t>8.SP.1, 8.SP.2, See eBook</t>
@@ -16381,7 +16837,7 @@
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16429,7 +16885,11 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr"/>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
           <t>8.EE.6, See eBook</t>
@@ -16437,7 +16897,7 @@
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16915,11 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr"/>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
           <t>8.EE.6, See eBook</t>
@@ -16463,7 +16927,7 @@
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16481,7 +16945,11 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr"/>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
           <t>8.EE.6, See eBook</t>
@@ -16489,7 +16957,7 @@
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -16759,7 +17227,11 @@
           <t>Simplifying Exponents (Properties of Exponents)</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr"/>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.4, 8.3.5.5, 8.3.6.4, 8.3.7.3</t>
+        </is>
+      </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
           <t>8.EE.1, See eBook</t>
@@ -16767,7 +17239,7 @@
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17479,11 @@
           <t>Right, Acute and Obtuse Triangles</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr"/>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
           <t>8.G.7, See eBook</t>
@@ -17015,7 +17491,7 @@
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -17033,7 +17509,11 @@
           <t>Right Triangles &amp; Pythagorean Theorem</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr"/>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
           <t>8.G.6, 8.G.7, See eBook</t>
@@ -17041,7 +17521,7 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -17059,7 +17539,11 @@
           <t>Square Root and Irrational Numbers</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr"/>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.6.2, 8.3.6.7, 8.3.6.8, 8.3.7.3</t>
+        </is>
+      </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
           <t>8.EE.2, 8.NS.2, See eBook</t>
@@ -17067,7 +17551,7 @@
       </c>
       <c r="F86" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -17085,7 +17569,11 @@
           <t>Rational vs. Irrational Numbers</t>
         </is>
       </c>
-      <c r="D87" s="13" t="inlineStr"/>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.6.2, 8.3.6.7, 8.3.6.8, 8.3.7.3</t>
+        </is>
+      </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
           <t>8.EE.2, 8.NS.1, See eBook</t>
@@ -17093,7 +17581,7 @@
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17599,11 @@
           <t>Pythagorean Theorem in Context</t>
         </is>
       </c>
-      <c r="D88" s="13" t="inlineStr"/>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
           <t>8.G.7, 8.G.8, See eBook</t>
@@ -17119,7 +17611,7 @@
       </c>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17629,11 @@
           <t>Pythagorean Theorem in 3-D</t>
         </is>
       </c>
-      <c r="D89" s="13" t="inlineStr"/>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
           <t>8.G.7, See eBook</t>
@@ -17145,7 +17641,7 @@
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -17293,7 +17789,11 @@
           <t>Volume of Sphere</t>
         </is>
       </c>
-      <c r="D95" s="13" t="inlineStr"/>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
           <t>8.G.9, See eBook</t>
@@ -17301,7 +17801,7 @@
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17819,11 @@
           <t>Volume in Context</t>
         </is>
       </c>
-      <c r="D96" s="13" t="inlineStr"/>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
       <c r="E96" s="19" t="inlineStr">
         <is>
           <t>8.G.9, See eBook</t>
@@ -17327,7 +17831,7 @@
       </c>
       <c r="F96" s="13" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
